--- a/data/trans_dic/P3A_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 19,4</t>
+          <t>14,87; 19,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 22,91</t>
+          <t>17,56; 22,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 24,99</t>
+          <t>18,73; 24,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 20,18</t>
+          <t>14,28; 20,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,88</t>
+          <t>5,99; 8,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,36</t>
+          <t>6,48; 9,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,31</t>
+          <t>6,65; 10,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,91</t>
+          <t>7,43; 10,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 13,11</t>
+          <t>10,39; 13,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,61</t>
+          <t>11,81; 14,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 15,9</t>
+          <t>12,42; 15,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 14,02</t>
+          <t>10,71; 13,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 23,08</t>
+          <t>19,06; 22,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 31,01</t>
+          <t>26,84; 30,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,71; 35,92</t>
+          <t>31,79; 35,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,54; 30,02</t>
+          <t>17,25; 29,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 13,44</t>
+          <t>10,18; 13,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,85; 18,48</t>
+          <t>14,97; 18,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,0</t>
+          <t>18,48; 22,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 23,83</t>
+          <t>15,5; 23,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 17,86</t>
+          <t>15,25; 17,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,59; 24,47</t>
+          <t>21,76; 24,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,6; 28,51</t>
+          <t>25,68; 28,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 26,25</t>
+          <t>18,68; 26,32</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,51; 31,61</t>
+          <t>23,83; 31,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 41,69</t>
+          <t>32,32; 42,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,18; 46,56</t>
+          <t>38,22; 46,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,09; 42,01</t>
+          <t>34,29; 41,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 29,75</t>
+          <t>21,65; 29,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 33,12</t>
+          <t>23,83; 33,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,28; 36,41</t>
+          <t>28,24; 36,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,17; 34,59</t>
+          <t>28,13; 34,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,83; 29,65</t>
+          <t>23,77; 29,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,36; 36,07</t>
+          <t>29,66; 35,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,45; 40,13</t>
+          <t>34,35; 40,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,98; 37,04</t>
+          <t>32,0; 37,06</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 22,27</t>
+          <t>19,56; 22,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 29,18</t>
+          <t>25,93; 28,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,87; 34,15</t>
+          <t>30,76; 34,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 29,68</t>
+          <t>20,7; 29,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,14</t>
+          <t>11,0; 13,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 16,2</t>
+          <t>13,61; 16,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,9</t>
+          <t>17,43; 19,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 21,92</t>
+          <t>16,16; 21,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,22</t>
+          <t>15,48; 17,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 22,24</t>
+          <t>20,1; 22,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,33; 26,36</t>
+          <t>24,26; 26,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 25,14</t>
+          <t>20,6; 25,03</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>153806; 200192</t>
+          <t>153385; 200279</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169830; 223088</t>
+          <t>170935; 221524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143660; 187831</t>
+          <t>140765; 186879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72727; 103911</t>
+          <t>73521; 105202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78091; 116676</t>
+          <t>78775; 115931</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84727; 125088</t>
+          <t>86687; 127352</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66136; 102339</t>
+          <t>65993; 100266</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56728; 82447</t>
+          <t>56160; 81128</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>246526; 307504</t>
+          <t>243829; 306270</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>271730; 337479</t>
+          <t>272939; 338057</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218429; 277293</t>
+          <t>216665; 276042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>136311; 178056</t>
+          <t>136109; 175825</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>321059; 390668</t>
+          <t>322517; 389001</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>525848; 608997</t>
+          <t>527086; 608693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>656738; 743902</t>
+          <t>658313; 744941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>424486; 687327</t>
+          <t>394805; 685188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163169; 213043</t>
+          <t>161398; 213236</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>260875; 324745</t>
+          <t>263069; 326617</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>363678; 436923</t>
+          <t>367037; 438971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>327510; 532977</t>
+          <t>346621; 534146</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>497770; 585398</t>
+          <t>499877; 587059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>803461; 910473</t>
+          <t>809606; 912960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1038866; 1156850</t>
+          <t>1042082; 1160195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>839336; 1187946</t>
+          <t>845573; 1191006</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>129619; 174300</t>
+          <t>131377; 174934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155464; 200586</t>
+          <t>155500; 202386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208416; 254194</t>
+          <t>208645; 256369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>220435; 271649</t>
+          <t>221724; 270865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>102661; 141372</t>
+          <t>102900; 141467</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109413; 151919</t>
+          <t>109272; 152540</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>155038; 199602</t>
+          <t>154831; 200810</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>186085; 228439</t>
+          <t>185762; 226033</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>244607; 304441</t>
+          <t>244058; 302746</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>275888; 338981</t>
+          <t>278715; 338073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376929; 439047</t>
+          <t>375780; 443145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>418020; 484115</t>
+          <t>418228; 484398</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>635310; 729493</t>
+          <t>640571; 736856</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>890749; 997745</t>
+          <t>886466; 989381</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1039843; 1150247</t>
+          <t>1036156; 1149815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>720248; 1024288</t>
+          <t>714371; 1021495</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>367940; 443267</t>
+          <t>371045; 445792</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>481568; 575339</t>
+          <t>483373; 573080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>608734; 701762</t>
+          <t>614861; 704700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>588826; 800478</t>
+          <t>590124; 800445</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1031181; 1145058</t>
+          <t>1029471; 1154499</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1404019; 1550651</t>
+          <t>1401412; 1543626</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1677993; 1817881</t>
+          <t>1673212; 1819054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1449910; 1785932</t>
+          <t>1463184; 1778026</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,41</t>
+          <t>14,94; 19,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 22,75</t>
+          <t>17,47; 22,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 24,86</t>
+          <t>18,83; 24,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 20,43</t>
+          <t>14,25; 20,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,82</t>
+          <t>6,08; 8,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,53</t>
+          <t>6,52; 9,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,1</t>
+          <t>6,56; 10,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,74</t>
+          <t>7,37; 10,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 13,06</t>
+          <t>10,32; 12,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 14,63</t>
+          <t>11,8; 14,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 15,83</t>
+          <t>12,45; 15,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 13,84</t>
+          <t>10,65; 13,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 22,98</t>
+          <t>19,29; 23,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,84; 30,99</t>
+          <t>26,82; 31,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,79; 35,97</t>
+          <t>31,67; 35,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 29,93</t>
+          <t>27,17; 31,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,45</t>
+          <t>10,24; 13,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 18,59</t>
+          <t>15,11; 18,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 22,1</t>
+          <t>18,35; 21,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,88</t>
+          <t>21,58; 24,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,91</t>
+          <t>15,27; 17,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,76; 24,54</t>
+          <t>21,71; 24,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 28,6</t>
+          <t>25,63; 28,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 26,32</t>
+          <t>24,91; 27,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,83; 31,73</t>
+          <t>23,48; 31,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,32; 42,06</t>
+          <t>32,22; 41,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,22; 46,96</t>
+          <t>37,83; 46,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,29; 41,89</t>
+          <t>34,68; 42,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,65; 29,77</t>
+          <t>21,35; 29,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,26</t>
+          <t>23,93; 32,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 36,63</t>
+          <t>28,41; 36,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,13; 34,22</t>
+          <t>27,02; 33,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,77; 29,49</t>
+          <t>23,65; 29,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,66; 35,97</t>
+          <t>29,13; 35,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,35; 40,5</t>
+          <t>34,16; 40,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,0; 37,06</t>
+          <t>31,96; 36,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,49</t>
+          <t>19,52; 22,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 28,94</t>
+          <t>26,1; 29,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,76; 34,13</t>
+          <t>30,73; 33,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 29,6</t>
+          <t>27,36; 30,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,21</t>
+          <t>10,89; 13,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 16,13</t>
+          <t>13,76; 16,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 19,98</t>
+          <t>17,22; 19,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,16; 21,91</t>
+          <t>20,34; 22,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,36</t>
+          <t>15,46; 17,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 22,14</t>
+          <t>20,05; 22,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,26; 26,38</t>
+          <t>24,22; 26,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 25,03</t>
+          <t>24,11; 26,12</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>97903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>72238</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>155506</t>
+          <t>170141</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>153385; 200279</t>
+          <t>154138; 201025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>170935; 221524</t>
+          <t>170131; 222375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140765; 186879</t>
+          <t>141553; 184213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73521; 105202</t>
+          <t>82458; 117737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78775; 115931</t>
+          <t>79837; 116595</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86687; 127352</t>
+          <t>87205; 126504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65993; 100266</t>
+          <t>65099; 100379</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56160; 81128</t>
+          <t>60587; 86919</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>243829; 306270</t>
+          <t>242103; 303081</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>272939; 338057</t>
+          <t>272541; 341164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216665; 276042</t>
+          <t>217213; 273972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>136109; 175825</t>
+          <t>149133; 192435</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>651692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>462534</t>
+          <t>503911</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1058896</t>
+          <t>1155603</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>322517; 389001</t>
+          <t>326463; 396012</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>527086; 608693</t>
+          <t>526769; 611714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658313; 744941</t>
+          <t>655906; 743279</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>394805; 685188</t>
+          <t>605770; 701549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>161398; 213236</t>
+          <t>162279; 213094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>263069; 326617</t>
+          <t>265479; 327052</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>367037; 438971</t>
+          <t>364511; 435954</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>346621; 534146</t>
+          <t>468217; 537633</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499877; 587059</t>
+          <t>500576; 586838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>809606; 912960</t>
+          <t>807957; 910111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1042082; 1160195</t>
+          <t>1039742; 1160315</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>845573; 1191006</t>
+          <t>1096040; 1212198</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245513</t>
+          <t>272541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>204985</t>
+          <t>220236</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>450498</t>
+          <t>492777</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131377; 174934</t>
+          <t>129476; 173540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155500; 202386</t>
+          <t>155049; 199416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208645; 256369</t>
+          <t>206521; 253593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221724; 270865</t>
+          <t>246774; 302014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>102900; 141467</t>
+          <t>101470; 140105</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109272; 152540</t>
+          <t>109746; 150582</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>154831; 200810</t>
+          <t>155764; 199239</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>185762; 226033</t>
+          <t>198586; 243695</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>244058; 302746</t>
+          <t>242767; 305373</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>278715; 338073</t>
+          <t>273789; 337358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>375780; 443145</t>
+          <t>373722; 439918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>418228; 484398</t>
+          <t>462304; 532519</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>930117</t>
+          <t>1022136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>734783</t>
+          <t>796384</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1664900</t>
+          <t>1818520</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>640571; 736856</t>
+          <t>639436; 734655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886466; 989381</t>
+          <t>892119; 998874</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1036156; 1149815</t>
+          <t>1035242; 1144253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>714371; 1021495</t>
+          <t>962868; 1080225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>371045; 445792</t>
+          <t>367576; 444153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>483373; 573080</t>
+          <t>488860; 573361</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>614861; 704700</t>
+          <t>607513; 700908</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>590124; 800445</t>
+          <t>757921; 838919</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1029471; 1154499</t>
+          <t>1027807; 1148678</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1401412; 1543626</t>
+          <t>1397417; 1540491</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1673212; 1819054</t>
+          <t>1670292; 1821511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1463184; 1778026</t>
+          <t>1746876; 1892981</t>
         </is>
       </c>
     </row>
